--- a/task3.xlsx
+++ b/task3.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Data Analytics\Excel\practice\task3\fact_table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Data Analytics\Excel\practice\task3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715DAEDB-80B4-4CB2-AFE4-7019E74C7B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D802C4-235D-4224-9889-D5DA86B3311D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="7" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet3!$A$4:$AE$4</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3057" uniqueCount="1662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3664" uniqueCount="1801">
   <si>
     <t>payment_key</t>
   </si>
@@ -5050,6 +5051,423 @@
   </si>
   <si>
     <t>Logical AND</t>
+  </si>
+  <si>
+    <t>I00001</t>
+  </si>
+  <si>
+    <t>A&amp;W Root Beer - 12 oz cans</t>
+  </si>
+  <si>
+    <t>a. Beverage - Soda</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Bolsius Boxmeer</t>
+  </si>
+  <si>
+    <t>A&amp;W Root Beer Diet - 12 oz cans</t>
+  </si>
+  <si>
+    <t>poland</t>
+  </si>
+  <si>
+    <t>CHROMADURLIN S.A.S</t>
+  </si>
+  <si>
+    <t>Barq's Root Beer - 12 oz cans</t>
+  </si>
+  <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>DENIMACH LTD</t>
+  </si>
+  <si>
+    <t>Cherry Coke 12oz</t>
+  </si>
+  <si>
+    <t>Cherry Coke Zero 12 pack</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>HARDFORD AB</t>
+  </si>
+  <si>
+    <t>Coke Classic 12 oz cans</t>
+  </si>
+  <si>
+    <t>Lithuania</t>
+  </si>
+  <si>
+    <t>BIGSO AB</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Indo Count Industries Ltd</t>
+  </si>
+  <si>
+    <t>Coke Zero Sugar 12 oz cans</t>
+  </si>
+  <si>
+    <t>Diet Coke - 12 oz cans</t>
+  </si>
+  <si>
+    <t>Diet Coke Caffeine Free 12oz cans</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Friedola 1888 GmbH</t>
+  </si>
+  <si>
+    <t>I00012</t>
+  </si>
+  <si>
+    <t>Diet Dr. Pepper - 12 oz cans</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>CHERRY GROUP CO.,LTD</t>
+  </si>
+  <si>
+    <t>Diet Gingerale 12 oz cans</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>MAESA SAS</t>
+  </si>
+  <si>
+    <t>Diet Mountain Dew 12oz cans</t>
+  </si>
+  <si>
+    <t>Diet Pepsi - 12 oz cans</t>
+  </si>
+  <si>
+    <t>I00016</t>
+  </si>
+  <si>
+    <t>Dr. Pepper - 12 oz cans</t>
+  </si>
+  <si>
+    <t>Fresca Black Cherry - 12 oz cans</t>
+  </si>
+  <si>
+    <t>Cambodia</t>
+  </si>
+  <si>
+    <t>NINGBO SEDUNO IMP &amp; EXP CO.LTD</t>
+  </si>
+  <si>
+    <t>Fresca Original - 12 oz cans</t>
+  </si>
+  <si>
+    <t>I00019</t>
+  </si>
+  <si>
+    <t>Fresca Peach Citrus - 12 oz cans</t>
+  </si>
+  <si>
+    <t>Ginger Ale - 12 oz cans</t>
+  </si>
+  <si>
+    <t>Hawaiian Punch - 12 oz cans</t>
+  </si>
+  <si>
+    <t>I00022</t>
+  </si>
+  <si>
+    <t>Mountain Dew - 12 oz cans</t>
+  </si>
+  <si>
+    <t>Pepsi - 12 oz cans</t>
+  </si>
+  <si>
+    <t>Seven Up - 12 oz cans</t>
+  </si>
+  <si>
+    <t>Sprite - 12 oz cans</t>
+  </si>
+  <si>
+    <t>Sprite Zero - 12 pack</t>
+  </si>
+  <si>
+    <t>Sunkist Orange - 12 oz cans</t>
+  </si>
+  <si>
+    <t>La Croix Sparkling Berry 12 ozv</t>
+  </si>
+  <si>
+    <t>a. Beverage Sparkling Water</t>
+  </si>
+  <si>
+    <t>I00031</t>
+  </si>
+  <si>
+    <t>La Croix Sparkling Coconut 12 oz</t>
+  </si>
+  <si>
+    <t>I00032</t>
+  </si>
+  <si>
+    <t>La Croix Sparkling Cran-Raspberry 12 oz</t>
+  </si>
+  <si>
+    <t>La Croix Sparkling Grapefruit 12 oz</t>
+  </si>
+  <si>
+    <t>La Croix Sparkling Lemon 12 oz</t>
+  </si>
+  <si>
+    <t>La Croix Sparkling Lime 12 oz</t>
+  </si>
+  <si>
+    <t>La Croix Sparkling Orange 12 oz</t>
+  </si>
+  <si>
+    <t>La Croix Sparkling Pure 12 oz</t>
+  </si>
+  <si>
+    <t>Perrier Flavors Sparkling Water 16.9oz</t>
+  </si>
+  <si>
+    <t>Perrier Sparkling Water glass 11oz</t>
+  </si>
+  <si>
+    <t>I00040</t>
+  </si>
+  <si>
+    <t>Perrier Sparkling Water plastic 16.9oz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pelligrino 16oz Plastic </t>
+  </si>
+  <si>
+    <t>Topo Chico 12 oz glass</t>
+  </si>
+  <si>
+    <t>Topo Chico 20oz plastic</t>
+  </si>
+  <si>
+    <t>Waterloo Sparkling Blackcherry 12oz</t>
+  </si>
+  <si>
+    <t>Waterloo Sparkling Grapefruit 12oz</t>
+  </si>
+  <si>
+    <t>Waterloo Sparkling Lemon 12oz</t>
+  </si>
+  <si>
+    <t>Waterloo Sparkling Lime 12oz</t>
+  </si>
+  <si>
+    <t>Waterloo Sparkling Mango 12oz</t>
+  </si>
+  <si>
+    <t>Waterloo Sparkling Original 12oz</t>
+  </si>
+  <si>
+    <t>Waterloo Sparkling Watermelon 12oz</t>
+  </si>
+  <si>
+    <t>Monster Java 15 oz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beverage - Energy/Protein </t>
+  </si>
+  <si>
+    <t>Monster Lo-Carb 16 oz</t>
+  </si>
+  <si>
+    <t>Beverage - Energy/Protein</t>
+  </si>
+  <si>
+    <t>Monster Original Green 16 oz</t>
+  </si>
+  <si>
+    <t>I00054</t>
+  </si>
+  <si>
+    <t>Monster Zero Ultra 16 oz</t>
+  </si>
+  <si>
+    <t>Monster Zero Ultra Variety 16 oz</t>
+  </si>
+  <si>
+    <t>Muscle Milk Protein Shake Choc. 11oz</t>
+  </si>
+  <si>
+    <t>I00057</t>
+  </si>
+  <si>
+    <t>Muscle Milk Protein Shake Van. 11oz</t>
+  </si>
+  <si>
+    <t>Premier Protein Shake Choc. 11oz</t>
+  </si>
+  <si>
+    <t>Muscle Milk Protein Shake Strbry. 11oz</t>
+  </si>
+  <si>
+    <t>Red Bull 12oz</t>
+  </si>
+  <si>
+    <t>Red Bull 16oz</t>
+  </si>
+  <si>
+    <t>Red Bull 8.4 oz</t>
+  </si>
+  <si>
+    <t>Red Bull Sugar Free 8.4 oz</t>
+  </si>
+  <si>
+    <t>G2 Lo Calorie Variety 20 oz</t>
+  </si>
+  <si>
+    <t>Beverage - Gatorade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gatorade Frost Variety 20 oz </t>
+  </si>
+  <si>
+    <t>Gatorade Lemon Lime 12oz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gatorade Liberty Variety 20 oz </t>
+  </si>
+  <si>
+    <t>Gatorade Frost Variety 12 oz</t>
+  </si>
+  <si>
+    <t>I00070</t>
+  </si>
+  <si>
+    <t>Gatorade Liberty Variety 12 oz</t>
+  </si>
+  <si>
+    <t>Gatorade Original Variety 12 oz</t>
+  </si>
+  <si>
+    <t>I00072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gatorade Variety 20 oz </t>
+  </si>
+  <si>
+    <t>Gatorade X-Factor Fierce Variety 20 oz</t>
+  </si>
+  <si>
+    <t>Gatorade Zero Variety 20 oz</t>
+  </si>
+  <si>
+    <t>Brisk Lemon Iced Tea - 12 oz cans</t>
+  </si>
+  <si>
+    <t>Beverage - Iced Tea</t>
+  </si>
+  <si>
+    <t>Diet Fuze Iced Tea</t>
+  </si>
+  <si>
+    <t>Fuze Iced Tea</t>
+  </si>
+  <si>
+    <t>Pure Leaf Sweet Tea 8.5oz</t>
+  </si>
+  <si>
+    <t>Pure Leaf Unsweetened Tea 18.5oz</t>
+  </si>
+  <si>
+    <t>Snapple Variety Pack 20oz</t>
+  </si>
+  <si>
+    <t>I00081</t>
+  </si>
+  <si>
+    <t>Tejava Unsweetened Black Tea 16.9oz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100% Juice Box Variety 6.75 oz </t>
+  </si>
+  <si>
+    <t>Beverage - Juice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocean Spray Cranberry Juice Cocktail 15oz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tropicana Apple Juice 10 oz 100% </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tropicana Orange Juice 10 oz 100% </t>
+  </si>
+  <si>
+    <t>V8 100% Vegetable Juice 11oz cans</t>
+  </si>
+  <si>
+    <t>I00087</t>
+  </si>
+  <si>
+    <t>V-8 Splash Variety 20 oz</t>
+  </si>
+  <si>
+    <t>Welch's 100% Juice Variety10 oz</t>
+  </si>
+  <si>
+    <t>AquaFina Purified Drinking Water 16oz</t>
+  </si>
+  <si>
+    <t>Beverage Water</t>
+  </si>
+  <si>
+    <t>Dasani Bottled Water 16.9 oz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nestle Purelife 16oz </t>
+  </si>
+  <si>
+    <t>Ozarka Spring Water 16.9 oz bottles</t>
+  </si>
+  <si>
+    <t>Ozarka Spring Water 20 oz</t>
+  </si>
+  <si>
+    <t>Ozarka Spring Water Mini 8oz</t>
+  </si>
+  <si>
+    <t>I00095</t>
+  </si>
+  <si>
+    <t>Propel Zero Variety 20 oz</t>
+  </si>
+  <si>
+    <t>botlltes</t>
+  </si>
+  <si>
+    <t>Sobe Zero Lifewater Variety 20 oz</t>
+  </si>
+  <si>
+    <t>item_name</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>man_country</t>
+  </si>
+  <si>
+    <t>supplier</t>
   </si>
 </sst>
 </file>
@@ -5081,7 +5499,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5124,6 +5542,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -5163,7 +5593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -5193,6 +5623,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -60390,4 +60822,6598 @@
   <autoFilter ref="A4:AE500" xr:uid="{9C1A1783-2E08-4609-A8AC-64621B6E489C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4B9406-9715-4075-AC6F-94256BAA4C7C}">
+  <dimension ref="A1:AE497"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1799</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>1800</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>1659</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>1661</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>1660</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="W1" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="X1" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z1" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA1" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB1" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="AC1" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AD1" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE1" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F2" s="9">
+        <v>1</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="15">
+        <v>11.5</v>
+      </c>
+      <c r="I2">
+        <f>H2*F2</f>
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F3" s="9">
+        <v>1</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I66" si="0">H3*F3</f>
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F4" s="9">
+        <v>8</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>1673</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F5" s="9">
+        <v>8</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F6" s="9">
+        <v>8</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>632</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F7" s="9">
+        <v>5</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="15">
+        <v>16.25</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>81.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F8" s="9">
+        <v>2</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F9" s="9">
+        <v>1</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="15">
+        <v>16.25</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>845</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F10" s="9">
+        <v>11</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="15">
+        <v>16.25</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>178.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F11" s="9">
+        <v>10</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="0"/>
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F12" s="9">
+        <v>8</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>1688</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F13" s="9">
+        <v>10</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="15">
+        <v>16.25</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="0"/>
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F14" s="9">
+        <v>3</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="0"/>
+        <v>20.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>922</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F15" s="9">
+        <v>6</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F16" s="9">
+        <v>3</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>20.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>1697</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F17" s="9">
+        <v>2</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="15">
+        <v>16.25</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>1698</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F18" s="9">
+        <v>9</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>60.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F19" s="9">
+        <v>9</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>60.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>1703</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F20" s="9">
+        <v>7</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>47.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
+        <v>798</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F21" s="9">
+        <v>4</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F22" s="9">
+        <v>4</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F23" s="9">
+        <v>7</v>
+      </c>
+      <c r="G23" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23" s="15">
+        <v>16.25</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>113.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F24" s="9">
+        <v>8</v>
+      </c>
+      <c r="G24" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>712</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>1708</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F25" s="9">
+        <v>1</v>
+      </c>
+      <c r="G25" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25" s="15">
+        <v>16.25</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="0"/>
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>948</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>1709</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F26" s="9">
+        <v>10</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="15">
+        <v>11.5</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C27" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F27" s="9">
+        <v>2</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>1710</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F28" s="9">
+        <v>8</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H28" s="15">
+        <v>16.25</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="0"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F29" s="9">
+        <v>1</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H29" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="0"/>
+        <v>6.75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>762</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F30" s="9">
+        <v>2</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H30" s="15">
+        <v>11.5</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F31" s="9">
+        <v>11</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H31" s="15">
+        <v>16</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="0"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F32" s="9">
+        <v>6</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H32" s="15">
+        <v>16</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F33" s="9">
+        <v>3</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H33" s="15">
+        <v>16</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F34" s="9">
+        <v>6</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H34" s="15">
+        <v>16</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="0"/>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
+        <v>838</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F35" s="9">
+        <v>3</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H35" s="15">
+        <v>16</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
+        <v>755</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>1721</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F36" s="9">
+        <v>11</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H36" s="15">
+        <v>16</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="0"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
+        <v>868</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F37" s="9">
+        <v>5</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H37" s="15">
+        <v>16</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E38" s="15" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F38" s="9">
+        <v>1</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H38" s="15">
+        <v>16</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="15" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F39" s="9">
+        <v>7</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H39" s="15">
+        <v>23</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="0"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="15" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F40" s="9">
+        <v>6</v>
+      </c>
+      <c r="G40" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H40" s="15">
+        <v>26</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="0"/>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F41" s="9">
+        <v>5</v>
+      </c>
+      <c r="G41" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H41" s="15">
+        <v>22</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="0"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="15" t="s">
+        <v>855</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>1728</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E42" s="15" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F42" s="9">
+        <v>11</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H42" s="15">
+        <v>23</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="0"/>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F43" s="9">
+        <v>5</v>
+      </c>
+      <c r="G43" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H43" s="15">
+        <v>28</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
+        <v>664</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F44" s="9">
+        <v>1</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H44" s="15">
+        <v>24</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F45" s="9">
+        <v>8</v>
+      </c>
+      <c r="G45" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H45" s="15">
+        <v>8</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F46" s="9">
+        <v>4</v>
+      </c>
+      <c r="G46" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H46" s="15">
+        <v>8</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="15" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>1733</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F47" s="9">
+        <v>10</v>
+      </c>
+      <c r="G47" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H47" s="15">
+        <v>8</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F48" s="9">
+        <v>3</v>
+      </c>
+      <c r="G48" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H48" s="15">
+        <v>8</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E49" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F49" s="9">
+        <v>1</v>
+      </c>
+      <c r="G49" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H49" s="15">
+        <v>8</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F50" s="9">
+        <v>10</v>
+      </c>
+      <c r="G50" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H50" s="15">
+        <v>8</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>1714</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F51" s="9">
+        <v>4</v>
+      </c>
+      <c r="G51" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H51" s="15">
+        <v>8</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="15" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E52" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F52" s="9">
+        <v>9</v>
+      </c>
+      <c r="G52" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H52" s="15">
+        <v>23</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="0"/>
+        <v>207</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="15" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F53" s="9">
+        <v>3</v>
+      </c>
+      <c r="G53" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H53" s="15">
+        <v>40</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F54" s="9">
+        <v>9</v>
+      </c>
+      <c r="G54" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H54" s="15">
+        <v>40</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="15" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>1744</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F55" s="9">
+        <v>11</v>
+      </c>
+      <c r="G55" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H55" s="15">
+        <v>40</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F56" s="9">
+        <v>7</v>
+      </c>
+      <c r="G56" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H56" s="15">
+        <v>40</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="0"/>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>1746</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F57" s="9">
+        <v>2</v>
+      </c>
+      <c r="G57" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H57" s="15">
+        <v>24</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="15" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F58" s="9">
+        <v>3</v>
+      </c>
+      <c r="G58" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H58" s="15">
+        <v>24</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>1749</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E59" s="15" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F59" s="9">
+        <v>9</v>
+      </c>
+      <c r="G59" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H59" s="15">
+        <v>22</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="0"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="15" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D60" s="15" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F60" s="9">
+        <v>1</v>
+      </c>
+      <c r="G60" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H60" s="15">
+        <v>22</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="15" t="s">
+        <v>539</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F61" s="9">
+        <v>3</v>
+      </c>
+      <c r="G61" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H61" s="15">
+        <v>22</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E62" s="15" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F62" s="9">
+        <v>3</v>
+      </c>
+      <c r="G62" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H62" s="15">
+        <v>55</v>
+      </c>
+      <c r="I62">
+        <f t="shared" si="0"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="15" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E63" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F63" s="9">
+        <v>11</v>
+      </c>
+      <c r="G63" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H63" s="15">
+        <v>37</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="0"/>
+        <v>407</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="15" t="s">
+        <v>609</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>1753</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E64" s="15" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F64" s="9">
+        <v>9</v>
+      </c>
+      <c r="G64" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H64" s="15">
+        <v>40</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>1741</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E65" s="15" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F65" s="9">
+        <v>3</v>
+      </c>
+      <c r="G65" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H65" s="15">
+        <v>40</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>1755</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D66" s="15" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F66" s="9">
+        <v>7</v>
+      </c>
+      <c r="G66" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H66" s="15">
+        <v>20</v>
+      </c>
+      <c r="I66">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F67" s="9">
+        <v>3</v>
+      </c>
+      <c r="G67" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H67" s="15">
+        <v>20</v>
+      </c>
+      <c r="I67">
+        <f t="shared" ref="I67:I130" si="1">H67*F67</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="15" t="s">
+        <v>939</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F68" s="9">
+        <v>8</v>
+      </c>
+      <c r="G68" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H68" s="15">
+        <v>8</v>
+      </c>
+      <c r="I68">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E69" s="15" t="s">
+        <v>1681</v>
+      </c>
+      <c r="F69" s="9">
+        <v>2</v>
+      </c>
+      <c r="G69" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H69" s="15">
+        <v>20</v>
+      </c>
+      <c r="I69">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F70" s="9">
+        <v>8</v>
+      </c>
+      <c r="G70" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H70" s="15">
+        <v>17.5</v>
+      </c>
+      <c r="I70">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="15" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F71" s="9">
+        <v>11</v>
+      </c>
+      <c r="G71" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H71" s="15">
+        <v>17.5</v>
+      </c>
+      <c r="I71">
+        <f t="shared" si="1"/>
+        <v>192.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F72" s="9">
+        <v>4</v>
+      </c>
+      <c r="G72" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H72" s="15">
+        <v>17.5</v>
+      </c>
+      <c r="I72">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="15" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F73" s="9">
+        <v>7</v>
+      </c>
+      <c r="G73" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H73" s="15">
+        <v>20</v>
+      </c>
+      <c r="I73">
+        <f t="shared" si="1"/>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F74" s="9">
+        <v>11</v>
+      </c>
+      <c r="G74" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H74" s="15">
+        <v>20</v>
+      </c>
+      <c r="I74">
+        <f t="shared" si="1"/>
+        <v>220</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="15" t="s">
+        <v>686</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F75" s="9">
+        <v>10</v>
+      </c>
+      <c r="G75" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H75" s="15">
+        <v>20</v>
+      </c>
+      <c r="I75">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C76" s="15" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>1692</v>
+      </c>
+      <c r="E76" s="15" t="s">
+        <v>1693</v>
+      </c>
+      <c r="F76" s="9">
+        <v>10</v>
+      </c>
+      <c r="G76" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H76" s="15">
+        <v>15.5</v>
+      </c>
+      <c r="I76">
+        <f t="shared" si="1"/>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F77" s="9">
+        <v>4</v>
+      </c>
+      <c r="G77" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H77" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I77">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E78" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F78" s="9">
+        <v>4</v>
+      </c>
+      <c r="G78" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H78" s="15">
+        <v>6.75</v>
+      </c>
+      <c r="I78">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E79" s="15" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F79" s="9">
+        <v>11</v>
+      </c>
+      <c r="G79" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H79" s="15">
+        <v>17</v>
+      </c>
+      <c r="I79">
+        <f t="shared" si="1"/>
+        <v>187</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D80" s="15" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E80" s="15" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F80" s="9">
+        <v>3</v>
+      </c>
+      <c r="G80" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H80" s="15">
+        <v>17</v>
+      </c>
+      <c r="I80">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E81" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F81" s="9">
+        <v>8</v>
+      </c>
+      <c r="G81" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H81" s="15">
+        <v>22</v>
+      </c>
+      <c r="I81">
+        <f t="shared" si="1"/>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="15" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>1776</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D82" s="15" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E82" s="15" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F82" s="9">
+        <v>7</v>
+      </c>
+      <c r="G82" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H82" s="15">
+        <v>29</v>
+      </c>
+      <c r="I82">
+        <f t="shared" si="1"/>
+        <v>203</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D83" s="15" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E83" s="15" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F83" s="9">
+        <v>1</v>
+      </c>
+      <c r="G83" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H83" s="15">
+        <v>15</v>
+      </c>
+      <c r="I83">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E84" s="15" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F84" s="9">
+        <v>8</v>
+      </c>
+      <c r="G84" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H84" s="15">
+        <v>14</v>
+      </c>
+      <c r="I84">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D85" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E85" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F85" s="9">
+        <v>4</v>
+      </c>
+      <c r="G85" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H85" s="15">
+        <v>18</v>
+      </c>
+      <c r="I85">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="15" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B86" s="15" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C86" s="15" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E86" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F86" s="9">
+        <v>6</v>
+      </c>
+      <c r="G86" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H86" s="15">
+        <v>18</v>
+      </c>
+      <c r="I86">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="15" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F87" s="9">
+        <v>8</v>
+      </c>
+      <c r="G87" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H87" s="15">
+        <v>18</v>
+      </c>
+      <c r="I87">
+        <f t="shared" si="1"/>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="15" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B88" s="15" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D88" s="15" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E88" s="15" t="s">
+        <v>1690</v>
+      </c>
+      <c r="F88" s="9">
+        <v>2</v>
+      </c>
+      <c r="G88" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H88" s="15">
+        <v>15</v>
+      </c>
+      <c r="I88">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C89" s="15" t="s">
+        <v>1778</v>
+      </c>
+      <c r="D89" s="15" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E89" s="15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F89" s="9">
+        <v>5</v>
+      </c>
+      <c r="G89" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H89" s="15">
+        <v>17</v>
+      </c>
+      <c r="I89">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="15" t="s">
+        <v>904</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D90" s="15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E90" s="15" t="s">
+        <v>1686</v>
+      </c>
+      <c r="F90" s="9">
+        <v>7</v>
+      </c>
+      <c r="G90" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H90" s="15">
+        <v>9</v>
+      </c>
+      <c r="I90">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="15" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C91" s="15" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E91" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F91" s="9">
+        <v>10</v>
+      </c>
+      <c r="G91" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H91" s="15">
+        <v>9</v>
+      </c>
+      <c r="I91">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B92" s="15" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C92" s="15" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D92" s="15" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E92" s="15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F92" s="9">
+        <v>1</v>
+      </c>
+      <c r="G92" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H92" s="15">
+        <v>7.5</v>
+      </c>
+      <c r="I92">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="15" t="s">
+        <v>546</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C93" s="15" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>1678</v>
+      </c>
+      <c r="E93" s="15" t="s">
+        <v>1679</v>
+      </c>
+      <c r="F93" s="9">
+        <v>6</v>
+      </c>
+      <c r="G93" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H93" s="15">
+        <v>10</v>
+      </c>
+      <c r="I93">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="15" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C94" s="15" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E94" s="15" t="s">
+        <v>1672</v>
+      </c>
+      <c r="F94" s="9">
+        <v>5</v>
+      </c>
+      <c r="G94" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H94" s="15">
+        <v>13</v>
+      </c>
+      <c r="I94">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="15" t="s">
+        <v>832</v>
+      </c>
+      <c r="B95" s="15" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C95" s="15" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D95" s="15" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E95" s="15" t="s">
+        <v>1666</v>
+      </c>
+      <c r="F95" s="9">
+        <v>6</v>
+      </c>
+      <c r="G95" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H95" s="15">
+        <v>11</v>
+      </c>
+      <c r="I95">
+        <f t="shared" si="1"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="15" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C96" s="15" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>1675</v>
+      </c>
+      <c r="E96" s="15" t="s">
+        <v>1676</v>
+      </c>
+      <c r="F96" s="9">
+        <v>1</v>
+      </c>
+      <c r="G96" s="15" t="s">
+        <v>1795</v>
+      </c>
+      <c r="H96" s="15">
+        <v>16</v>
+      </c>
+      <c r="I96">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="15" t="s">
+        <v>576</v>
+      </c>
+      <c r="B97" s="15" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C97" s="15" t="s">
+        <v>1787</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>1699</v>
+      </c>
+      <c r="E97" s="15" t="s">
+        <v>1700</v>
+      </c>
+      <c r="F97" s="9">
+        <v>2</v>
+      </c>
+      <c r="G97" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H97" s="15">
+        <v>20</v>
+      </c>
+      <c r="I97">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F98" s="9">
+        <v>11</v>
+      </c>
+      <c r="I98">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F99" s="9">
+        <v>8</v>
+      </c>
+      <c r="I99">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F100" s="9">
+        <v>10</v>
+      </c>
+      <c r="I100">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F101" s="9">
+        <v>4</v>
+      </c>
+      <c r="I101">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F102" s="9">
+        <v>4</v>
+      </c>
+      <c r="I102">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F103" s="9">
+        <v>1</v>
+      </c>
+      <c r="I103">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F104" s="9">
+        <v>8</v>
+      </c>
+      <c r="I104">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F105" s="9">
+        <v>7</v>
+      </c>
+      <c r="I105">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F106" s="9">
+        <v>9</v>
+      </c>
+      <c r="I106">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F107" s="9">
+        <v>8</v>
+      </c>
+      <c r="I107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F108" s="9">
+        <v>1</v>
+      </c>
+      <c r="I108">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F109" s="9">
+        <v>3</v>
+      </c>
+      <c r="I109">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F110" s="9">
+        <v>3</v>
+      </c>
+      <c r="I110">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F111" s="9">
+        <v>5</v>
+      </c>
+      <c r="I111">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F112" s="9">
+        <v>10</v>
+      </c>
+      <c r="I112">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F113" s="9">
+        <v>11</v>
+      </c>
+      <c r="I113">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F114" s="9">
+        <v>3</v>
+      </c>
+      <c r="I114">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F115" s="9">
+        <v>11</v>
+      </c>
+      <c r="I115">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F116" s="9">
+        <v>7</v>
+      </c>
+      <c r="I116">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F117" s="9">
+        <v>2</v>
+      </c>
+      <c r="I117">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F118" s="9">
+        <v>8</v>
+      </c>
+      <c r="I118">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F119" s="9">
+        <v>11</v>
+      </c>
+      <c r="I119">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F120" s="9">
+        <v>11</v>
+      </c>
+      <c r="I120">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F121" s="9">
+        <v>10</v>
+      </c>
+      <c r="I121">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F122" s="9">
+        <v>8</v>
+      </c>
+      <c r="I122">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F123" s="9">
+        <v>11</v>
+      </c>
+      <c r="I123">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F124" s="9">
+        <v>11</v>
+      </c>
+      <c r="I124">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F125" s="9">
+        <v>2</v>
+      </c>
+      <c r="I125">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F126" s="9">
+        <v>5</v>
+      </c>
+      <c r="I126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F127" s="9">
+        <v>1</v>
+      </c>
+      <c r="I127">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F128" s="9">
+        <v>11</v>
+      </c>
+      <c r="I128">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F129" s="9">
+        <v>8</v>
+      </c>
+      <c r="I129">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F130" s="9">
+        <v>1</v>
+      </c>
+      <c r="I130">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F131" s="9">
+        <v>2</v>
+      </c>
+      <c r="I131">
+        <f t="shared" ref="I131:I194" si="2">H131*F131</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F132" s="9">
+        <v>5</v>
+      </c>
+      <c r="I132">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F133" s="9">
+        <v>4</v>
+      </c>
+      <c r="I133">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F134" s="9">
+        <v>7</v>
+      </c>
+      <c r="I134">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F135" s="9">
+        <v>6</v>
+      </c>
+      <c r="I135">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F136" s="9">
+        <v>8</v>
+      </c>
+      <c r="I136">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F137" s="9">
+        <v>9</v>
+      </c>
+      <c r="I137">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F138" s="9">
+        <v>5</v>
+      </c>
+      <c r="I138">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F139" s="9">
+        <v>7</v>
+      </c>
+      <c r="I139">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F140" s="9">
+        <v>5</v>
+      </c>
+      <c r="I140">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F141" s="9">
+        <v>7</v>
+      </c>
+      <c r="I141">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F142" s="9">
+        <v>2</v>
+      </c>
+      <c r="I142">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F143" s="9">
+        <v>5</v>
+      </c>
+      <c r="I143">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F144" s="9">
+        <v>9</v>
+      </c>
+      <c r="I144">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F145" s="9">
+        <v>6</v>
+      </c>
+      <c r="I145">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F146" s="9">
+        <v>2</v>
+      </c>
+      <c r="I146">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F147" s="9">
+        <v>3</v>
+      </c>
+      <c r="I147">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F148" s="9">
+        <v>6</v>
+      </c>
+      <c r="I148">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F149" s="9">
+        <v>7</v>
+      </c>
+      <c r="I149">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F150" s="9">
+        <v>2</v>
+      </c>
+      <c r="I150">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F151" s="9">
+        <v>4</v>
+      </c>
+      <c r="I151">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F152" s="9">
+        <v>3</v>
+      </c>
+      <c r="I152">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F153" s="9">
+        <v>10</v>
+      </c>
+      <c r="I153">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F154" s="9">
+        <v>2</v>
+      </c>
+      <c r="I154">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F155" s="9">
+        <v>8</v>
+      </c>
+      <c r="I155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F156" s="9">
+        <v>2</v>
+      </c>
+      <c r="I156">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F157" s="9">
+        <v>5</v>
+      </c>
+      <c r="I157">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F158" s="9">
+        <v>2</v>
+      </c>
+      <c r="I158">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F159" s="9">
+        <v>11</v>
+      </c>
+      <c r="I159">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F160" s="9">
+        <v>2</v>
+      </c>
+      <c r="I160">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F161" s="9">
+        <v>1</v>
+      </c>
+      <c r="I161">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F162" s="9">
+        <v>7</v>
+      </c>
+      <c r="I162">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F163" s="9">
+        <v>2</v>
+      </c>
+      <c r="I163">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F164" s="9">
+        <v>2</v>
+      </c>
+      <c r="I164">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F165" s="9">
+        <v>1</v>
+      </c>
+      <c r="I165">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F166" s="9">
+        <v>4</v>
+      </c>
+      <c r="I166">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F167" s="9">
+        <v>4</v>
+      </c>
+      <c r="I167">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F168" s="9">
+        <v>6</v>
+      </c>
+      <c r="I168">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F169" s="9">
+        <v>3</v>
+      </c>
+      <c r="I169">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F170" s="9">
+        <v>7</v>
+      </c>
+      <c r="I170">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F171" s="9">
+        <v>4</v>
+      </c>
+      <c r="I171">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F172" s="9">
+        <v>8</v>
+      </c>
+      <c r="I172">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F173" s="9">
+        <v>9</v>
+      </c>
+      <c r="I173">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F174" s="9">
+        <v>8</v>
+      </c>
+      <c r="I174">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F175" s="9">
+        <v>8</v>
+      </c>
+      <c r="I175">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F176" s="9">
+        <v>11</v>
+      </c>
+      <c r="I176">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F177" s="9">
+        <v>3</v>
+      </c>
+      <c r="I177">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F178" s="9">
+        <v>5</v>
+      </c>
+      <c r="I178">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F179" s="9">
+        <v>6</v>
+      </c>
+      <c r="I179">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F180" s="9">
+        <v>9</v>
+      </c>
+      <c r="I180">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F181" s="9">
+        <v>10</v>
+      </c>
+      <c r="I181">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F182" s="9">
+        <v>2</v>
+      </c>
+      <c r="I182">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F183" s="9">
+        <v>6</v>
+      </c>
+      <c r="I183">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F184" s="9">
+        <v>8</v>
+      </c>
+      <c r="I184">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F185" s="9">
+        <v>4</v>
+      </c>
+      <c r="I185">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F186" s="9">
+        <v>9</v>
+      </c>
+      <c r="I186">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F187" s="9">
+        <v>6</v>
+      </c>
+      <c r="I187">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F188" s="9">
+        <v>3</v>
+      </c>
+      <c r="I188">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F189" s="9">
+        <v>4</v>
+      </c>
+      <c r="I189">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F190" s="9">
+        <v>6</v>
+      </c>
+      <c r="I190">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F191" s="9">
+        <v>4</v>
+      </c>
+      <c r="I191">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F192" s="9">
+        <v>4</v>
+      </c>
+      <c r="I192">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F193" s="9">
+        <v>3</v>
+      </c>
+      <c r="I193">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F194" s="9">
+        <v>10</v>
+      </c>
+      <c r="I194">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F195" s="9">
+        <v>4</v>
+      </c>
+      <c r="I195">
+        <f t="shared" ref="I195:I258" si="3">H195*F195</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F196" s="9">
+        <v>11</v>
+      </c>
+      <c r="I196">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F197" s="9">
+        <v>6</v>
+      </c>
+      <c r="I197">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F198" s="9">
+        <v>6</v>
+      </c>
+      <c r="I198">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F199" s="9">
+        <v>9</v>
+      </c>
+      <c r="I199">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F200" s="9">
+        <v>8</v>
+      </c>
+      <c r="I200">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F201" s="9">
+        <v>7</v>
+      </c>
+      <c r="I201">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F202" s="9">
+        <v>9</v>
+      </c>
+      <c r="I202">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F203" s="9">
+        <v>6</v>
+      </c>
+      <c r="I203">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F204" s="9">
+        <v>8</v>
+      </c>
+      <c r="I204">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F205" s="9">
+        <v>6</v>
+      </c>
+      <c r="I205">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F206" s="9">
+        <v>5</v>
+      </c>
+      <c r="I206">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F207" s="9">
+        <v>8</v>
+      </c>
+      <c r="I207">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F208" s="9">
+        <v>10</v>
+      </c>
+      <c r="I208">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F209" s="9">
+        <v>9</v>
+      </c>
+      <c r="I209">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F210" s="9">
+        <v>3</v>
+      </c>
+      <c r="I210">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F211" s="9">
+        <v>2</v>
+      </c>
+      <c r="I211">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F212" s="9">
+        <v>4</v>
+      </c>
+      <c r="I212">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F213" s="9">
+        <v>6</v>
+      </c>
+      <c r="I213">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F214" s="9">
+        <v>1</v>
+      </c>
+      <c r="I214">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F215" s="9">
+        <v>4</v>
+      </c>
+      <c r="I215">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F216" s="9">
+        <v>10</v>
+      </c>
+      <c r="I216">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F217" s="9">
+        <v>7</v>
+      </c>
+      <c r="I217">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F218" s="9">
+        <v>11</v>
+      </c>
+      <c r="I218">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F219" s="9">
+        <v>4</v>
+      </c>
+      <c r="I219">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F220" s="9">
+        <v>10</v>
+      </c>
+      <c r="I220">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F221" s="9">
+        <v>5</v>
+      </c>
+      <c r="I221">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F222" s="9">
+        <v>5</v>
+      </c>
+      <c r="I222">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F223" s="9">
+        <v>11</v>
+      </c>
+      <c r="I223">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F224" s="9">
+        <v>2</v>
+      </c>
+      <c r="I224">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F225" s="9">
+        <v>8</v>
+      </c>
+      <c r="I225">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F226" s="9">
+        <v>2</v>
+      </c>
+      <c r="I226">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F227" s="9">
+        <v>7</v>
+      </c>
+      <c r="I227">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F228" s="9">
+        <v>7</v>
+      </c>
+      <c r="I228">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F229" s="9">
+        <v>4</v>
+      </c>
+      <c r="I229">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F230" s="9">
+        <v>8</v>
+      </c>
+      <c r="I230">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F231" s="9">
+        <v>4</v>
+      </c>
+      <c r="I231">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F232" s="9">
+        <v>3</v>
+      </c>
+      <c r="I232">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F233" s="9">
+        <v>5</v>
+      </c>
+      <c r="I233">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F234" s="9">
+        <v>3</v>
+      </c>
+      <c r="I234">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F235" s="9">
+        <v>10</v>
+      </c>
+      <c r="I235">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F236" s="9">
+        <v>3</v>
+      </c>
+      <c r="I236">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F237" s="9">
+        <v>5</v>
+      </c>
+      <c r="I237">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F238" s="9">
+        <v>10</v>
+      </c>
+      <c r="I238">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F239" s="9">
+        <v>4</v>
+      </c>
+      <c r="I239">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F240" s="9">
+        <v>10</v>
+      </c>
+      <c r="I240">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F241" s="9">
+        <v>2</v>
+      </c>
+      <c r="I241">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F242" s="9">
+        <v>3</v>
+      </c>
+      <c r="I242">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F243" s="9">
+        <v>1</v>
+      </c>
+      <c r="I243">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F244" s="9">
+        <v>9</v>
+      </c>
+      <c r="I244">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F245" s="9">
+        <v>5</v>
+      </c>
+      <c r="I245">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F246" s="9">
+        <v>9</v>
+      </c>
+      <c r="I246">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F247" s="9">
+        <v>5</v>
+      </c>
+      <c r="I247">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F248" s="9">
+        <v>8</v>
+      </c>
+      <c r="I248">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F249" s="9">
+        <v>10</v>
+      </c>
+      <c r="I249">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F250" s="9">
+        <v>7</v>
+      </c>
+      <c r="I250">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F251" s="9">
+        <v>11</v>
+      </c>
+      <c r="I251">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F252" s="9">
+        <v>10</v>
+      </c>
+      <c r="I252">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F253" s="9">
+        <v>8</v>
+      </c>
+      <c r="I253">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F254" s="9">
+        <v>7</v>
+      </c>
+      <c r="I254">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F255" s="9">
+        <v>8</v>
+      </c>
+      <c r="I255">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F256" s="9">
+        <v>6</v>
+      </c>
+      <c r="I256">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F257" s="9">
+        <v>8</v>
+      </c>
+      <c r="I257">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F258" s="9">
+        <v>6</v>
+      </c>
+      <c r="I258">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F259" s="9">
+        <v>10</v>
+      </c>
+      <c r="I259">
+        <f t="shared" ref="I259:I322" si="4">H259*F259</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F260" s="9">
+        <v>10</v>
+      </c>
+      <c r="I260">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F261" s="9">
+        <v>5</v>
+      </c>
+      <c r="I261">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F262" s="9">
+        <v>10</v>
+      </c>
+      <c r="I262">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F263" s="9">
+        <v>1</v>
+      </c>
+      <c r="I263">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F264" s="9">
+        <v>7</v>
+      </c>
+      <c r="I264">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F265" s="9">
+        <v>5</v>
+      </c>
+      <c r="I265">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F266" s="9">
+        <v>11</v>
+      </c>
+      <c r="I266">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F267" s="9">
+        <v>8</v>
+      </c>
+      <c r="I267">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F268" s="9">
+        <v>6</v>
+      </c>
+      <c r="I268">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F269" s="9">
+        <v>4</v>
+      </c>
+      <c r="I269">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F270" s="9">
+        <v>3</v>
+      </c>
+      <c r="I270">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F271" s="9">
+        <v>7</v>
+      </c>
+      <c r="I271">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F272" s="9">
+        <v>4</v>
+      </c>
+      <c r="I272">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F273" s="9">
+        <v>5</v>
+      </c>
+      <c r="I273">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F274" s="9">
+        <v>6</v>
+      </c>
+      <c r="I274">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F275" s="9">
+        <v>3</v>
+      </c>
+      <c r="I275">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F276" s="9">
+        <v>4</v>
+      </c>
+      <c r="I276">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F277" s="9">
+        <v>6</v>
+      </c>
+      <c r="I277">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F278" s="9">
+        <v>3</v>
+      </c>
+      <c r="I278">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F279" s="9">
+        <v>1</v>
+      </c>
+      <c r="I279">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F280" s="9">
+        <v>8</v>
+      </c>
+      <c r="I280">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F281" s="9">
+        <v>4</v>
+      </c>
+      <c r="I281">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F282" s="9">
+        <v>11</v>
+      </c>
+      <c r="I282">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F283" s="9">
+        <v>6</v>
+      </c>
+      <c r="I283">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F284" s="9">
+        <v>5</v>
+      </c>
+      <c r="I284">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F285" s="9">
+        <v>6</v>
+      </c>
+      <c r="I285">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F286" s="9">
+        <v>11</v>
+      </c>
+      <c r="I286">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F287" s="9">
+        <v>9</v>
+      </c>
+      <c r="I287">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F288" s="9">
+        <v>1</v>
+      </c>
+      <c r="I288">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F289" s="9">
+        <v>1</v>
+      </c>
+      <c r="I289">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F290" s="9">
+        <v>9</v>
+      </c>
+      <c r="I290">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F291" s="9">
+        <v>3</v>
+      </c>
+      <c r="I291">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F292" s="9">
+        <v>6</v>
+      </c>
+      <c r="I292">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F293" s="9">
+        <v>5</v>
+      </c>
+      <c r="I293">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F294" s="9">
+        <v>1</v>
+      </c>
+      <c r="I294">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F295" s="9">
+        <v>10</v>
+      </c>
+      <c r="I295">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F296" s="9">
+        <v>1</v>
+      </c>
+      <c r="I296">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F297" s="9">
+        <v>1</v>
+      </c>
+      <c r="I297">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F298" s="9">
+        <v>2</v>
+      </c>
+      <c r="I298">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F299" s="9">
+        <v>3</v>
+      </c>
+      <c r="I299">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F300" s="9">
+        <v>7</v>
+      </c>
+      <c r="I300">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F301" s="9">
+        <v>6</v>
+      </c>
+      <c r="I301">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F302" s="9">
+        <v>9</v>
+      </c>
+      <c r="I302">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F303" s="9">
+        <v>5</v>
+      </c>
+      <c r="I303">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F304" s="9">
+        <v>5</v>
+      </c>
+      <c r="I304">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F305" s="9">
+        <v>5</v>
+      </c>
+      <c r="I305">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F306" s="9">
+        <v>6</v>
+      </c>
+      <c r="I306">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F307" s="9">
+        <v>7</v>
+      </c>
+      <c r="I307">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F308" s="9">
+        <v>6</v>
+      </c>
+      <c r="I308">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F309" s="9">
+        <v>5</v>
+      </c>
+      <c r="I309">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F310" s="9">
+        <v>2</v>
+      </c>
+      <c r="I310">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F311" s="9">
+        <v>3</v>
+      </c>
+      <c r="I311">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F312" s="9">
+        <v>8</v>
+      </c>
+      <c r="I312">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F313" s="9">
+        <v>1</v>
+      </c>
+      <c r="I313">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F314" s="9">
+        <v>4</v>
+      </c>
+      <c r="I314">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F315" s="9">
+        <v>4</v>
+      </c>
+      <c r="I315">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F316" s="9">
+        <v>9</v>
+      </c>
+      <c r="I316">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F317" s="9">
+        <v>9</v>
+      </c>
+      <c r="I317">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F318" s="9">
+        <v>3</v>
+      </c>
+      <c r="I318">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F319" s="9">
+        <v>7</v>
+      </c>
+      <c r="I319">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F320" s="9">
+        <v>5</v>
+      </c>
+      <c r="I320">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F321" s="9">
+        <v>10</v>
+      </c>
+      <c r="I321">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F322" s="9">
+        <v>5</v>
+      </c>
+      <c r="I322">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F323" s="9">
+        <v>4</v>
+      </c>
+      <c r="I323">
+        <f t="shared" ref="I323:I386" si="5">H323*F323</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F324" s="9">
+        <v>10</v>
+      </c>
+      <c r="I324">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F325" s="9">
+        <v>1</v>
+      </c>
+      <c r="I325">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F326" s="9">
+        <v>7</v>
+      </c>
+      <c r="I326">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F327" s="9">
+        <v>11</v>
+      </c>
+      <c r="I327">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F328" s="9">
+        <v>3</v>
+      </c>
+      <c r="I328">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F329" s="9">
+        <v>11</v>
+      </c>
+      <c r="I329">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F330" s="9">
+        <v>9</v>
+      </c>
+      <c r="I330">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F331" s="9">
+        <v>5</v>
+      </c>
+      <c r="I331">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F332" s="9">
+        <v>10</v>
+      </c>
+      <c r="I332">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F333" s="9">
+        <v>4</v>
+      </c>
+      <c r="I333">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F334" s="9">
+        <v>4</v>
+      </c>
+      <c r="I334">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F335" s="9">
+        <v>7</v>
+      </c>
+      <c r="I335">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F336" s="9">
+        <v>11</v>
+      </c>
+      <c r="I336">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F337" s="9">
+        <v>2</v>
+      </c>
+      <c r="I337">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F338" s="9">
+        <v>6</v>
+      </c>
+      <c r="I338">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F339" s="9">
+        <v>2</v>
+      </c>
+      <c r="I339">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F340" s="9">
+        <v>5</v>
+      </c>
+      <c r="I340">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F341" s="9">
+        <v>3</v>
+      </c>
+      <c r="I341">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F342" s="9">
+        <v>7</v>
+      </c>
+      <c r="I342">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F343" s="9">
+        <v>4</v>
+      </c>
+      <c r="I343">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F344" s="9">
+        <v>8</v>
+      </c>
+      <c r="I344">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F345" s="9">
+        <v>11</v>
+      </c>
+      <c r="I345">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F346" s="9">
+        <v>11</v>
+      </c>
+      <c r="I346">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F347" s="9">
+        <v>4</v>
+      </c>
+      <c r="I347">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F348" s="9">
+        <v>5</v>
+      </c>
+      <c r="I348">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F349" s="9">
+        <v>10</v>
+      </c>
+      <c r="I349">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F350" s="9">
+        <v>4</v>
+      </c>
+      <c r="I350">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F351" s="9">
+        <v>7</v>
+      </c>
+      <c r="I351">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F352" s="9">
+        <v>11</v>
+      </c>
+      <c r="I352">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F353" s="9">
+        <v>10</v>
+      </c>
+      <c r="I353">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F354" s="9">
+        <v>1</v>
+      </c>
+      <c r="I354">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F355" s="9">
+        <v>7</v>
+      </c>
+      <c r="I355">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F356" s="9">
+        <v>11</v>
+      </c>
+      <c r="I356">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F357" s="9">
+        <v>6</v>
+      </c>
+      <c r="I357">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F358" s="9">
+        <v>11</v>
+      </c>
+      <c r="I358">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F359" s="9">
+        <v>8</v>
+      </c>
+      <c r="I359">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F360" s="9">
+        <v>1</v>
+      </c>
+      <c r="I360">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F361" s="9">
+        <v>1</v>
+      </c>
+      <c r="I361">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F362" s="9">
+        <v>6</v>
+      </c>
+      <c r="I362">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F363" s="9">
+        <v>8</v>
+      </c>
+      <c r="I363">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F364" s="9">
+        <v>11</v>
+      </c>
+      <c r="I364">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F365" s="9">
+        <v>2</v>
+      </c>
+      <c r="I365">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F366" s="9">
+        <v>8</v>
+      </c>
+      <c r="I366">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F367" s="9">
+        <v>5</v>
+      </c>
+      <c r="I367">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F368" s="9">
+        <v>8</v>
+      </c>
+      <c r="I368">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F369" s="9">
+        <v>11</v>
+      </c>
+      <c r="I369">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F370" s="9">
+        <v>11</v>
+      </c>
+      <c r="I370">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F371" s="9">
+        <v>8</v>
+      </c>
+      <c r="I371">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F372" s="9">
+        <v>7</v>
+      </c>
+      <c r="I372">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F373" s="9">
+        <v>7</v>
+      </c>
+      <c r="I373">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F374" s="9">
+        <v>9</v>
+      </c>
+      <c r="I374">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F375" s="9">
+        <v>9</v>
+      </c>
+      <c r="I375">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F376" s="9">
+        <v>2</v>
+      </c>
+      <c r="I376">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F377" s="9">
+        <v>9</v>
+      </c>
+      <c r="I377">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F378" s="9">
+        <v>6</v>
+      </c>
+      <c r="I378">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F379" s="9">
+        <v>3</v>
+      </c>
+      <c r="I379">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F380" s="9">
+        <v>5</v>
+      </c>
+      <c r="I380">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F381" s="9">
+        <v>6</v>
+      </c>
+      <c r="I381">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F382" s="9">
+        <v>6</v>
+      </c>
+      <c r="I382">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F383" s="9">
+        <v>11</v>
+      </c>
+      <c r="I383">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F384" s="9">
+        <v>1</v>
+      </c>
+      <c r="I384">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F385" s="9">
+        <v>11</v>
+      </c>
+      <c r="I385">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F386" s="9">
+        <v>11</v>
+      </c>
+      <c r="I386">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F387" s="9">
+        <v>8</v>
+      </c>
+      <c r="I387">
+        <f t="shared" ref="I387:I450" si="6">H387*F387</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F388" s="9">
+        <v>5</v>
+      </c>
+      <c r="I388">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F389" s="9">
+        <v>1</v>
+      </c>
+      <c r="I389">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F390" s="9">
+        <v>7</v>
+      </c>
+      <c r="I390">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F391" s="9">
+        <v>5</v>
+      </c>
+      <c r="I391">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F392" s="9">
+        <v>8</v>
+      </c>
+      <c r="I392">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F393" s="9">
+        <v>11</v>
+      </c>
+      <c r="I393">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F394" s="9">
+        <v>7</v>
+      </c>
+      <c r="I394">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F395" s="9">
+        <v>8</v>
+      </c>
+      <c r="I395">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F396" s="9">
+        <v>8</v>
+      </c>
+      <c r="I396">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F397" s="9">
+        <v>2</v>
+      </c>
+      <c r="I397">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F398" s="9">
+        <v>5</v>
+      </c>
+      <c r="I398">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F399" s="9">
+        <v>9</v>
+      </c>
+      <c r="I399">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F400" s="9">
+        <v>5</v>
+      </c>
+      <c r="I400">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F401" s="9">
+        <v>2</v>
+      </c>
+      <c r="I401">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F402" s="9">
+        <v>4</v>
+      </c>
+      <c r="I402">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F403" s="9">
+        <v>4</v>
+      </c>
+      <c r="I403">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F404" s="9">
+        <v>8</v>
+      </c>
+      <c r="I404">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F405" s="9">
+        <v>3</v>
+      </c>
+      <c r="I405">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F406" s="9">
+        <v>3</v>
+      </c>
+      <c r="I406">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F407" s="9">
+        <v>10</v>
+      </c>
+      <c r="I407">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F408" s="9">
+        <v>10</v>
+      </c>
+      <c r="I408">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F409" s="9">
+        <v>4</v>
+      </c>
+      <c r="I409">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F410" s="9">
+        <v>6</v>
+      </c>
+      <c r="I410">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F411" s="9">
+        <v>1</v>
+      </c>
+      <c r="I411">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F412" s="9">
+        <v>4</v>
+      </c>
+      <c r="I412">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F413" s="9">
+        <v>8</v>
+      </c>
+      <c r="I413">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F414" s="9">
+        <v>3</v>
+      </c>
+      <c r="I414">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F415" s="9">
+        <v>1</v>
+      </c>
+      <c r="I415">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F416" s="9">
+        <v>7</v>
+      </c>
+      <c r="I416">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F417" s="9">
+        <v>7</v>
+      </c>
+      <c r="I417">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F418" s="9">
+        <v>11</v>
+      </c>
+      <c r="I418">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F419" s="9">
+        <v>11</v>
+      </c>
+      <c r="I419">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F420" s="9">
+        <v>10</v>
+      </c>
+      <c r="I420">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F421" s="9">
+        <v>10</v>
+      </c>
+      <c r="I421">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F422" s="9">
+        <v>4</v>
+      </c>
+      <c r="I422">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F423" s="9">
+        <v>4</v>
+      </c>
+      <c r="I423">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F424" s="9">
+        <v>3</v>
+      </c>
+      <c r="I424">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F425" s="9">
+        <v>3</v>
+      </c>
+      <c r="I425">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F426" s="9">
+        <v>11</v>
+      </c>
+      <c r="I426">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F427" s="9">
+        <v>2</v>
+      </c>
+      <c r="I427">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F428" s="9">
+        <v>5</v>
+      </c>
+      <c r="I428">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F429" s="9">
+        <v>11</v>
+      </c>
+      <c r="I429">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F430" s="9">
+        <v>6</v>
+      </c>
+      <c r="I430">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F431" s="9">
+        <v>3</v>
+      </c>
+      <c r="I431">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F432" s="9">
+        <v>5</v>
+      </c>
+      <c r="I432">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F433" s="9">
+        <v>5</v>
+      </c>
+      <c r="I433">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F434" s="9">
+        <v>4</v>
+      </c>
+      <c r="I434">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F435" s="9">
+        <v>8</v>
+      </c>
+      <c r="I435">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F436" s="9">
+        <v>6</v>
+      </c>
+      <c r="I436">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F437" s="9">
+        <v>9</v>
+      </c>
+      <c r="I437">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F438" s="9">
+        <v>7</v>
+      </c>
+      <c r="I438">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F439" s="9">
+        <v>9</v>
+      </c>
+      <c r="I439">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F440" s="9">
+        <v>8</v>
+      </c>
+      <c r="I440">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F441" s="9">
+        <v>7</v>
+      </c>
+      <c r="I441">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F442" s="9">
+        <v>4</v>
+      </c>
+      <c r="I442">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F443" s="9">
+        <v>2</v>
+      </c>
+      <c r="I443">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F444" s="9">
+        <v>3</v>
+      </c>
+      <c r="I444">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F445" s="9">
+        <v>10</v>
+      </c>
+      <c r="I445">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F446" s="9">
+        <v>11</v>
+      </c>
+      <c r="I446">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F447" s="9">
+        <v>7</v>
+      </c>
+      <c r="I447">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F448" s="9">
+        <v>8</v>
+      </c>
+      <c r="I448">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F449" s="9">
+        <v>9</v>
+      </c>
+      <c r="I449">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F450" s="9">
+        <v>3</v>
+      </c>
+      <c r="I450">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F451" s="9">
+        <v>4</v>
+      </c>
+      <c r="I451">
+        <f t="shared" ref="I451:I497" si="7">H451*F451</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F452" s="9">
+        <v>1</v>
+      </c>
+      <c r="I452">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F453" s="9">
+        <v>6</v>
+      </c>
+      <c r="I453">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F454" s="9">
+        <v>9</v>
+      </c>
+      <c r="I454">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F455" s="9">
+        <v>11</v>
+      </c>
+      <c r="I455">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F456" s="9">
+        <v>3</v>
+      </c>
+      <c r="I456">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F457" s="9">
+        <v>7</v>
+      </c>
+      <c r="I457">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F458" s="9">
+        <v>10</v>
+      </c>
+      <c r="I458">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F459" s="9">
+        <v>8</v>
+      </c>
+      <c r="I459">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F460" s="9">
+        <v>5</v>
+      </c>
+      <c r="I460">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F461" s="9">
+        <v>7</v>
+      </c>
+      <c r="I461">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F462" s="9">
+        <v>9</v>
+      </c>
+      <c r="I462">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F463" s="9">
+        <v>10</v>
+      </c>
+      <c r="I463">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F464" s="9">
+        <v>5</v>
+      </c>
+      <c r="I464">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F465" s="9">
+        <v>8</v>
+      </c>
+      <c r="I465">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F466" s="9">
+        <v>4</v>
+      </c>
+      <c r="I466">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F467" s="9">
+        <v>3</v>
+      </c>
+      <c r="I467">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F468" s="9">
+        <v>6</v>
+      </c>
+      <c r="I468">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F469" s="9">
+        <v>5</v>
+      </c>
+      <c r="I469">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F470" s="9">
+        <v>7</v>
+      </c>
+      <c r="I470">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F471" s="9">
+        <v>10</v>
+      </c>
+      <c r="I471">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F472" s="9">
+        <v>10</v>
+      </c>
+      <c r="I472">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F473" s="9">
+        <v>6</v>
+      </c>
+      <c r="I473">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F474" s="9">
+        <v>1</v>
+      </c>
+      <c r="I474">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F475" s="9">
+        <v>4</v>
+      </c>
+      <c r="I475">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F476" s="9">
+        <v>11</v>
+      </c>
+      <c r="I476">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F477" s="9">
+        <v>9</v>
+      </c>
+      <c r="I477">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F478" s="9">
+        <v>7</v>
+      </c>
+      <c r="I478">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F479" s="9">
+        <v>8</v>
+      </c>
+      <c r="I479">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F480" s="9">
+        <v>9</v>
+      </c>
+      <c r="I480">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F481" s="9">
+        <v>4</v>
+      </c>
+      <c r="I481">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F482" s="9">
+        <v>8</v>
+      </c>
+      <c r="I482">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F483" s="9">
+        <v>5</v>
+      </c>
+      <c r="I483">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F484" s="9">
+        <v>2</v>
+      </c>
+      <c r="I484">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F485" s="9">
+        <v>6</v>
+      </c>
+      <c r="I485">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F486" s="9">
+        <v>6</v>
+      </c>
+      <c r="I486">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F487" s="9">
+        <v>5</v>
+      </c>
+      <c r="I487">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F488" s="9">
+        <v>2</v>
+      </c>
+      <c r="I488">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F489" s="9">
+        <v>5</v>
+      </c>
+      <c r="I489">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F490" s="9">
+        <v>11</v>
+      </c>
+      <c r="I490">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F491" s="9">
+        <v>7</v>
+      </c>
+      <c r="I491">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F492" s="9">
+        <v>1</v>
+      </c>
+      <c r="I492">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F493" s="9">
+        <v>5</v>
+      </c>
+      <c r="I493">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="494" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F494" s="9">
+        <v>9</v>
+      </c>
+      <c r="I494">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="495" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F495" s="9">
+        <v>10</v>
+      </c>
+      <c r="I495">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F496" s="9">
+        <v>3</v>
+      </c>
+      <c r="I496">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="6:9" x14ac:dyDescent="0.25">
+      <c r="F497" s="9">
+        <v>4</v>
+      </c>
+      <c r="I497">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>